--- a/data/trans_orig/P16A11-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A11-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4366</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3684</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>490185</t>
+          <t>490135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>465657</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>467489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>957869</t>
+          <t>957187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13686</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>730088</t>
+          <t>729261</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>615195</t>
+          <t>614771</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>623736</t>
+          <t>623735</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1347296</t>
+          <t>1347944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1358205</t>
+          <t>1358210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25853</t>
+          <t>25451</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19260</t>
+          <t>19484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40040</t>
+          <t>40023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33913</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59260</t>
+          <t>59112</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>611796</t>
+          <t>612198</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627199</t>
+          <t>628129</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>649704</t>
+          <t>649721</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>670484</t>
+          <t>670260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1268134</t>
+          <t>1268282</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1293481</t>
+          <t>1294405</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51571</t>
+          <t>51712</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83158</t>
+          <t>83097</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42227</t>
+          <t>41673</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70737</t>
+          <t>69127</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102301</t>
+          <t>102115</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141163</t>
+          <t>144288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>435989</t>
+          <t>436050</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>467576</t>
+          <t>467435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>444905</t>
+          <t>446515</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473415</t>
+          <t>473969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>893626</t>
+          <t>890501</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>932488</t>
+          <t>932674</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99990</t>
+          <t>99876</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136043</t>
+          <t>136330</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112042</t>
+          <t>113999</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148307</t>
+          <t>149823</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>221302</t>
+          <t>221586</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>275517</t>
+          <t>272698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>250667</t>
+          <t>250380</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>286720</t>
+          <t>286834</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>255679</t>
+          <t>254163</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>291944</t>
+          <t>289987</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>515179</t>
+          <t>517998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>569394</t>
+          <t>569110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96329</t>
+          <t>97698</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>129781</t>
+          <t>129091</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>139901</t>
+          <t>138700</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>174803</t>
+          <t>172851</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>246743</t>
+          <t>246456</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>292983</t>
+          <t>295168</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,45%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>162802</t>
+          <t>163492</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196254</t>
+          <t>194885</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>168131</t>
+          <t>170083</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>203033</t>
+          <t>204234</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>342534</t>
+          <t>340349</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>388774</t>
+          <t>389061</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,22%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85188</t>
+          <t>85245</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>113226</t>
+          <t>114145</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>169479</t>
+          <t>169179</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>206868</t>
+          <t>207915</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>260200</t>
+          <t>261641</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>307902</t>
+          <t>309660</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,94%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96657</t>
+          <t>95738</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124695</t>
+          <t>124638</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127040</t>
+          <t>125993</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>164429</t>
+          <t>164729</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>235889</t>
+          <t>234131</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283591</t>
+          <t>282150</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,89%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>379776</t>
+          <t>379184</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>455223</t>
+          <t>449429</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>520780</t>
+          <t>525033</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>611006</t>
+          <t>608714</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>920899</t>
+          <t>922669</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1037997</t>
+          <t>1040186</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2820302</t>
+          <t>2826096</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2895749</t>
+          <t>2896341</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2768191</t>
+          <t>2770483</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2858417</t>
+          <t>2854164</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5616725</t>
+          <t>5614536</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5733823</t>
+          <t>5732053</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,62 +3747,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1958</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4559</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7100</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447721</t>
+          <t>448276</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427381</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>875345</t>
+          <t>877886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17593</t>
+          <t>16823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8003</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27278</t>
+          <t>26515</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>672102</t>
+          <t>672416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>683408</t>
+          <t>683887</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>591621</t>
+          <t>592391</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>605416</t>
+          <t>605395</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1268173</t>
+          <t>1268936</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1287448</t>
+          <t>1286768</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21346</t>
+          <t>21267</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43636</t>
+          <t>43897</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>14555</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33004</t>
+          <t>33033</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40359</t>
+          <t>39853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70246</t>
+          <t>71099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636418</t>
+          <t>636157</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658708</t>
+          <t>658787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>672931</t>
+          <t>672902</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>691493</t>
+          <t>691380</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1315743</t>
+          <t>1314890</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1345630</t>
+          <t>1346136</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56574</t>
+          <t>56212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91070</t>
+          <t>89400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65702</t>
+          <t>65505</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101145</t>
+          <t>101241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>129698</t>
+          <t>131288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178671</t>
+          <t>177235</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>523547</t>
+          <t>525217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>558043</t>
+          <t>558405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>512927</t>
+          <t>512831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>548370</t>
+          <t>548567</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1050018</t>
+          <t>1051454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1098991</t>
+          <t>1097401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130993</t>
+          <t>131622</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171578</t>
+          <t>173531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>158031</t>
+          <t>157881</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>199876</t>
+          <t>200390</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>300967</t>
+          <t>299854</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>360133</t>
+          <t>361394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>256766</t>
+          <t>254813</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>297351</t>
+          <t>296722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>246799</t>
+          <t>246285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>288644</t>
+          <t>288794</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>514885</t>
+          <t>513624</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>574051</t>
+          <t>575164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,73%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>139533</t>
+          <t>138712</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175576</t>
+          <t>176534</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>181012</t>
+          <t>181676</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>219375</t>
+          <t>221393</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>333383</t>
+          <t>333032</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>386145</t>
+          <t>384670</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,95%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134210</t>
+          <t>133252</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>170253</t>
+          <t>171074</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134621</t>
+          <t>132603</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172984</t>
+          <t>172320</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>277637</t>
+          <t>279112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>330399</t>
+          <t>330750</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130107</t>
+          <t>131033</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164280</t>
+          <t>164659</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>230468</t>
+          <t>229743</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>269951</t>
+          <t>269040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>372590</t>
+          <t>375218</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>425088</t>
+          <t>425634</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,75%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85571</t>
+          <t>85192</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>119744</t>
+          <t>118818</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>117845</t>
+          <t>118756</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>157328</t>
+          <t>158053</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>212559</t>
+          <t>212013</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>265057</t>
+          <t>262429</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,16%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>521960</t>
+          <t>527150</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>617425</t>
+          <t>617562</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>695928</t>
+          <t>693845</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>791566</t>
+          <t>796944</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1243721</t>
+          <t>1249357</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1377777</t>
+          <t>1382581</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2804569</t>
+          <t>2804432</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2900034</t>
+          <t>2894844</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2755462</t>
+          <t>2750084</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2851100</t>
+          <t>2853183</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5591244</t>
+          <t>5586440</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5725300</t>
+          <t>5719664</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,97 +6691,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4524</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>902</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4531</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4533</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3999</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>391224</t>
+          <t>391231</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>811219</t>
+          <t>810685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>14733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>577423</t>
+          <t>578248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588551</t>
+          <t>588521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556885</t>
+          <t>556873</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1138454</t>
+          <t>1139307</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1151103</t>
+          <t>1151110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31016</t>
+          <t>31839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24572</t>
+          <t>25153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25961</t>
+          <t>27269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50321</t>
+          <t>52028</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>638081</t>
+          <t>637258</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656080</t>
+          <t>655809</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636814</t>
+          <t>636233</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>652553</t>
+          <t>652661</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1280162</t>
+          <t>1278455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1304522</t>
+          <t>1303214</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73053</t>
+          <t>73478</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108268</t>
+          <t>110753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46429</t>
+          <t>47372</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77341</t>
+          <t>76798</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>126878</t>
+          <t>127187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174794</t>
+          <t>177019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>537780</t>
+          <t>535295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>572995</t>
+          <t>572570</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>571736</t>
+          <t>572279</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>602648</t>
+          <t>601705</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1120331</t>
+          <t>1118106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1168247</t>
+          <t>1167938</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,18%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89122</t>
+          <t>87710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127200</t>
+          <t>126670</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129407</t>
+          <t>128414</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>172308</t>
+          <t>173481</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227598</t>
+          <t>229194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>287074</t>
+          <t>286474</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>350718</t>
+          <t>351248</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>388796</t>
+          <t>390208</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>324541</t>
+          <t>323368</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>367442</t>
+          <t>368435</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>687693</t>
+          <t>688293</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>747169</t>
+          <t>745573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,49%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>122224</t>
+          <t>122761</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>161277</t>
+          <t>159091</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>150995</t>
+          <t>150866</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>189324</t>
+          <t>191747</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>285201</t>
+          <t>284906</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>337878</t>
+          <t>338614</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>173053</t>
+          <t>175239</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>212106</t>
+          <t>211569</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188438</t>
+          <t>186015</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226767</t>
+          <t>226896</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>374214</t>
+          <t>373478</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>426891</t>
+          <t>427186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,99%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126216</t>
+          <t>127962</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>155457</t>
+          <t>155896</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>207510</t>
+          <t>205531</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>250187</t>
+          <t>252847</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>343726</t>
+          <t>344181</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>395374</t>
+          <t>398402</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,62%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101541</t>
+          <t>101102</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>130782</t>
+          <t>129036</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>149982</t>
+          <t>147322</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>192659</t>
+          <t>194638</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>261793</t>
+          <t>258765</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>313441</t>
+          <t>312986</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,63%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>464438</t>
+          <t>464682</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>550516</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>582339</t>
+          <t>582402</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>677238</t>
+          <t>675898</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1072519</t>
+          <t>1071688</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1202296</t>
+          <t>1196193</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2847771</t>
+          <t>2843834</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2929912</t>
+          <t>2929668</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2867304</t>
+          <t>2868644</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2962203</t>
+          <t>2962140</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5736596</t>
+          <t>5742699</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5866373</t>
+          <t>5867204</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,56%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para la tensión arterial en las dos últimas semanas en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>399086</t>
+          <t>399134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305226</t>
+          <t>304308</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>702952</t>
+          <t>702836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713029</t>
+          <t>713187</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,98%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7135</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416412</t>
+          <t>416474</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500738</t>
+          <t>500706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509880</t>
+          <t>510243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>921860</t>
+          <t>921603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>932422</t>
+          <t>932112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29343</t>
+          <t>28896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17036</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>20740</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40362</t>
+          <t>41259</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506995</t>
+          <t>507442</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>524620</t>
+          <t>525245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>525432</t>
+          <t>525315</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>535976</t>
+          <t>535847</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1038444</t>
+          <t>1037547</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1057812</t>
+          <t>1058066</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41598</t>
+          <t>41867</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141196</t>
+          <t>141651</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69646</t>
+          <t>69967</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105141</t>
+          <t>105161</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107566</t>
+          <t>116261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225258</t>
+          <t>227922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>746590</t>
+          <t>746135</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>846188</t>
+          <t>845919</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>607740</t>
+          <t>607720</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>643235</t>
+          <t>642914</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1375409</t>
+          <t>1372745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1493101</t>
+          <t>1484406</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140265</t>
+          <t>139375</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181164</t>
+          <t>178763</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123745</t>
+          <t>123626</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>152587</t>
+          <t>153292</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>274141</t>
+          <t>272195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>321833</t>
+          <t>320704</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,02%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>379073</t>
+          <t>381474</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>419972</t>
+          <t>420862</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>392300</t>
+          <t>391595</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>421142</t>
+          <t>421261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>783291</t>
+          <t>784420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>830983</t>
+          <t>832929</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>159504</t>
+          <t>159256</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>189318</t>
+          <t>190114</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>267297</t>
+          <t>268241</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>513650</t>
+          <t>506462</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>448424</t>
+          <t>443040</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>776384</t>
+          <t>756366</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>77,52%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>177964</t>
+          <t>177168</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207778</t>
+          <t>208026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94718</t>
+          <t>101906</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>341071</t>
+          <t>340127</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>199266</t>
+          <t>219284</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>527226</t>
+          <t>532610</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,59%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>150079</t>
+          <t>148369</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>175055</t>
+          <t>175837</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>259934</t>
+          <t>260709</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>287901</t>
+          <t>289147</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>416989</t>
+          <t>418088</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>457233</t>
+          <t>458257</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,77%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>107704</t>
+          <t>106922</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>132680</t>
+          <t>134390</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136824</t>
+          <t>135578</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>164791</t>
+          <t>164016</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>250251</t>
+          <t>249227</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>290495</t>
+          <t>289396</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>472651</t>
+          <t>468711</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>678362</t>
+          <t>672069</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>724417</t>
+          <t>721775</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1439981</t>
+          <t>1386413</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1316310</t>
+          <t>1305539</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2143246</t>
+          <t>2162816</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2779575</t>
+          <t>2785868</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2985286</t>
+          <t>2989226</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2218052</t>
+          <t>2271620</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2933616</t>
+          <t>2936258</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4972723</t>
+          <t>4953153</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5799659</t>
+          <t>5810430</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A11-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A11-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>490135</t>
+          <t>490101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>957187</t>
+          <t>958172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>7073</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>13890</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>729261</t>
+          <t>728416</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>614771</t>
+          <t>614888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>623735</t>
+          <t>623648</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1347944</t>
+          <t>1347092</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1358210</t>
+          <t>1358240</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9520</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25451</t>
+          <t>25774</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>19224</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40023</t>
+          <t>39764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32989</t>
+          <t>32635</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59112</t>
+          <t>60324</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>612198</t>
+          <t>611875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628129</t>
+          <t>627704</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>649721</t>
+          <t>649980</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>670260</t>
+          <t>670520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1268282</t>
+          <t>1267070</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1294405</t>
+          <t>1294759</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51712</t>
+          <t>50994</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83097</t>
+          <t>82371</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>41273</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69127</t>
+          <t>69078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102115</t>
+          <t>101065</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>144288</t>
+          <t>141950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>436050</t>
+          <t>436776</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>467435</t>
+          <t>468153</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>446515</t>
+          <t>446564</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473969</t>
+          <t>474369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>890501</t>
+          <t>892839</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>932674</t>
+          <t>933724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99876</t>
+          <t>99115</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136330</t>
+          <t>137466</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113999</t>
+          <t>112561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149823</t>
+          <t>150096</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>221586</t>
+          <t>222684</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>272698</t>
+          <t>275708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>250380</t>
+          <t>249244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>286834</t>
+          <t>287595</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>254163</t>
+          <t>253890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>289987</t>
+          <t>291425</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>517998</t>
+          <t>514988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>569110</t>
+          <t>568012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,84%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97698</t>
+          <t>96891</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>129091</t>
+          <t>129311</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>138700</t>
+          <t>139289</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172851</t>
+          <t>175065</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>246456</t>
+          <t>246958</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>295168</t>
+          <t>293703</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163492</t>
+          <t>163272</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>194885</t>
+          <t>195692</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>170083</t>
+          <t>167869</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>204234</t>
+          <t>203645</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>340349</t>
+          <t>341814</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>389061</t>
+          <t>388559</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85245</t>
+          <t>83730</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>114145</t>
+          <t>112724</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>169179</t>
+          <t>168114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>207915</t>
+          <t>205387</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>261641</t>
+          <t>262302</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>309660</t>
+          <t>309575</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95738</t>
+          <t>97159</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124638</t>
+          <t>126153</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>125993</t>
+          <t>128521</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>164729</t>
+          <t>165794</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>234131</t>
+          <t>234216</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>282150</t>
+          <t>281489</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>379184</t>
+          <t>380247</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>449429</t>
+          <t>452546</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>525033</t>
+          <t>524789</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>608714</t>
+          <t>611644</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>922669</t>
+          <t>915783</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1040186</t>
+          <t>1028937</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2826096</t>
+          <t>2822979</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2896341</t>
+          <t>2895278</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2770483</t>
+          <t>2767553</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2854164</t>
+          <t>2854408</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5614536</t>
+          <t>5625785</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5732053</t>
+          <t>5738939</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,24%</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448276</t>
+          <t>448758</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>877886</t>
+          <t>877623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16823</t>
+          <t>17639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8683</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26515</t>
+          <t>26614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>672416</t>
+          <t>671447</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>683887</t>
+          <t>683360</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>592391</t>
+          <t>591575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>605395</t>
+          <t>605546</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1268936</t>
+          <t>1268837</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1286768</t>
+          <t>1286906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21267</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43897</t>
+          <t>44271</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14555</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33033</t>
+          <t>33701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39853</t>
+          <t>39848</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71099</t>
+          <t>69399</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636157</t>
+          <t>635783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658787</t>
+          <t>659459</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>672902</t>
+          <t>672234</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>691380</t>
+          <t>691015</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1314890</t>
+          <t>1316590</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1346136</t>
+          <t>1346141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56212</t>
+          <t>57350</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89400</t>
+          <t>90007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65505</t>
+          <t>66601</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101241</t>
+          <t>100687</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131288</t>
+          <t>131605</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177235</t>
+          <t>180121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>525217</t>
+          <t>524610</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>558405</t>
+          <t>557267</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>512831</t>
+          <t>513385</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>548567</t>
+          <t>547471</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1051454</t>
+          <t>1048568</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1097401</t>
+          <t>1097084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,29%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>131622</t>
+          <t>132579</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>173531</t>
+          <t>174548</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>157881</t>
+          <t>156535</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>200390</t>
+          <t>199443</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>299854</t>
+          <t>301163</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>361394</t>
+          <t>361993</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>254813</t>
+          <t>253796</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>296722</t>
+          <t>295765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>246285</t>
+          <t>247232</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>288794</t>
+          <t>290140</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>513624</t>
+          <t>513025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>575164</t>
+          <t>573855</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>138712</t>
+          <t>139772</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>176534</t>
+          <t>178316</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>181676</t>
+          <t>183565</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>221393</t>
+          <t>220366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>333032</t>
+          <t>332639</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>384670</t>
+          <t>384473</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>133252</t>
+          <t>131470</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>171074</t>
+          <t>170014</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>132603</t>
+          <t>133630</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172320</t>
+          <t>170431</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>279112</t>
+          <t>279309</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>330750</t>
+          <t>331143</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,89%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131033</t>
+          <t>132990</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164659</t>
+          <t>165751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>229743</t>
+          <t>230173</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>269040</t>
+          <t>268589</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>375218</t>
+          <t>375741</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>425634</t>
+          <t>424775</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,62%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85192</t>
+          <t>84100</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>118818</t>
+          <t>116861</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118756</t>
+          <t>119207</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>158053</t>
+          <t>157623</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>212013</t>
+          <t>212872</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>262429</t>
+          <t>261906</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>527150</t>
+          <t>526209</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>617562</t>
+          <t>616452</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>693845</t>
+          <t>690133</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>796944</t>
+          <t>794399</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1249357</t>
+          <t>1249622</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1382581</t>
+          <t>1381315</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2804432</t>
+          <t>2805542</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2894844</t>
+          <t>2895785</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2750084</t>
+          <t>2752629</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2853183</t>
+          <t>2856895</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5586440</t>
+          <t>5587706</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5719664</t>
+          <t>5719399</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>391231</t>
+          <t>391230</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810685</t>
+          <t>811032</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12248</t>
+          <t>12733</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14733</t>
+          <t>15429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>578248</t>
+          <t>577763</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588521</t>
+          <t>588546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556873</t>
+          <t>557138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1139307</t>
+          <t>1138611</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1151110</t>
+          <t>1150472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13288</t>
+          <t>12713</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31839</t>
+          <t>32062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25153</t>
+          <t>25205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27269</t>
+          <t>25853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52028</t>
+          <t>49751</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>637258</t>
+          <t>637035</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655809</t>
+          <t>656384</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636233</t>
+          <t>636181</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>652661</t>
+          <t>651902</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1278455</t>
+          <t>1280732</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1303214</t>
+          <t>1304630</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73478</t>
+          <t>69613</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110753</t>
+          <t>107004</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47372</t>
+          <t>47283</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76798</t>
+          <t>79059</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127187</t>
+          <t>127301</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177019</t>
+          <t>174863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>535295</t>
+          <t>539044</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>572570</t>
+          <t>576435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>572279</t>
+          <t>570018</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>601705</t>
+          <t>601794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1118106</t>
+          <t>1120262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1167938</t>
+          <t>1167824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,17%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87710</t>
+          <t>88455</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126670</t>
+          <t>127707</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173481</t>
+          <t>170592</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>229194</t>
+          <t>228523</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>286474</t>
+          <t>285085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>351248</t>
+          <t>350211</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>390208</t>
+          <t>389463</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>323368</t>
+          <t>326257</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>688293</t>
+          <t>689682</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>745573</t>
+          <t>746244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,56%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>122761</t>
+          <t>122810</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>159091</t>
+          <t>157925</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>150866</t>
+          <t>151678</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>191747</t>
+          <t>191074</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>284906</t>
+          <t>282454</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>338614</t>
+          <t>336869</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,31%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>175239</t>
+          <t>176405</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211569</t>
+          <t>211520</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186015</t>
+          <t>186688</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226896</t>
+          <t>226084</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>373478</t>
+          <t>375223</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>427186</t>
+          <t>429638</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,33%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>127962</t>
+          <t>126280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>155896</t>
+          <t>154845</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>205531</t>
+          <t>204974</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>252847</t>
+          <t>249788</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>344181</t>
+          <t>342332</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>398402</t>
+          <t>395891</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101102</t>
+          <t>102153</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>129036</t>
+          <t>130718</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147322</t>
+          <t>150381</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>194638</t>
+          <t>195195</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>258765</t>
+          <t>261276</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>312986</t>
+          <t>314835</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,91%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>464682</t>
+          <t>460657</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>550516</t>
+          <t>542765</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>582402</t>
+          <t>581873</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>675898</t>
+          <t>681888</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1071688</t>
+          <t>1072991</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1196193</t>
+          <t>1201570</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2843834</t>
+          <t>2851585</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2929668</t>
+          <t>2933693</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2868644</t>
+          <t>2862654</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2962140</t>
+          <t>2962669</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5742699</t>
+          <t>5737322</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5867204</t>
+          <t>5865901</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>16211</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399818</t>
+          <t>404957</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>399134</t>
+          <t>393355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,27 +9813,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>311579</t>
+          <t>360480</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304308</t>
+          <t>352337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>711397</t>
+          <t>765437</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>702836</t>
+          <t>754094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,17 +10043,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>13779</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421568</t>
+          <t>474760</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>416474</t>
+          <t>470003</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,17 +10156,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>506871</t>
+          <t>496526</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500706</t>
+          <t>490697</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510243</t>
+          <t>499288</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>928439</t>
+          <t>971286</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>921603</t>
+          <t>964194</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>932112</t>
+          <t>975029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18593</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28896</t>
+          <t>33797</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17153</t>
+          <t>19297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29469</t>
+          <t>34960</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>24467</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41259</t>
+          <t>47310</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>517745</t>
+          <t>598452</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>507442</t>
+          <t>587040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525245</t>
+          <t>607253</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>531592</t>
+          <t>609564</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>525315</t>
+          <t>602842</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>535847</t>
+          <t>614606</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1049337</t>
+          <t>1208016</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1037547</t>
+          <t>1195666</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1058066</t>
+          <t>1218509</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95251</t>
+          <t>98393</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41867</t>
+          <t>82484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141651</t>
+          <t>118470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85389</t>
+          <t>89723</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69967</t>
+          <t>76617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105161</t>
+          <t>105256</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>180640</t>
+          <t>188116</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116261</t>
+          <t>166667</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227922</t>
+          <t>214616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>792535</t>
+          <t>602224</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>746135</t>
+          <t>582147</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>845919</t>
+          <t>618133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>627492</t>
+          <t>647163</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>607720</t>
+          <t>631630</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>642914</t>
+          <t>660269</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1420027</t>
+          <t>1249388</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1372745</t>
+          <t>1222888</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1484406</t>
+          <t>1270837</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>158793</t>
+          <t>168719</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139375</t>
+          <t>150016</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>178763</t>
+          <t>191218</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>137169</t>
+          <t>156242</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123626</t>
+          <t>141069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>153292</t>
+          <t>172442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>295962</t>
+          <t>324961</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>272195</t>
+          <t>297756</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320704</t>
+          <t>351688</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>401444</t>
+          <t>439640</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>381474</t>
+          <t>417141</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>420862</t>
+          <t>458343</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>407718</t>
+          <t>451206</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>391595</t>
+          <t>435006</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>421261</t>
+          <t>466379</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>809162</t>
+          <t>890846</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>784420</t>
+          <t>864119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>832929</t>
+          <t>918051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,51%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>175550</t>
+          <t>190262</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>159256</t>
+          <t>172532</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>190114</t>
+          <t>207254</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>388067</t>
+          <t>202412</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>268241</t>
+          <t>187773</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>506462</t>
+          <t>218657</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>563617</t>
+          <t>392675</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>443040</t>
+          <t>369304</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>756366</t>
+          <t>413471</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>191732</t>
+          <t>215896</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>177168</t>
+          <t>198904</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208026</t>
+          <t>233626</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>220301</t>
+          <t>236754</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101906</t>
+          <t>220509</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>340127</t>
+          <t>251393</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>412033</t>
+          <t>452649</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>219284</t>
+          <t>431853</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532610</t>
+          <t>476020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>56,31%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367282</t>
+          <t>406158</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367282</t>
+          <t>406158</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367282</t>
+          <t>406158</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>975650</t>
+          <t>845324</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>975650</t>
+          <t>845324</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>975650</t>
+          <t>845324</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>163003</t>
+          <t>178354</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148369</t>
+          <t>164161</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>175837</t>
+          <t>193157</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>274886</t>
+          <t>298680</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>260709</t>
+          <t>283153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>289147</t>
+          <t>313444</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,22 +11793,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>437889</t>
+          <t>477035</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>418088</t>
+          <t>457194</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>458257</t>
+          <t>499379</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,55%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>119756</t>
+          <t>131844</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>106922</t>
+          <t>117041</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>134390</t>
+          <t>146037</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>149839</t>
+          <t>164730</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>135578</t>
+          <t>149966</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>164016</t>
+          <t>180257</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,27 +11906,27 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>269595</t>
+          <t>296573</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>249227</t>
+          <t>274229</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>289396</t>
+          <t>316414</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>613339</t>
+          <t>663080</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>468711</t>
+          <t>618741</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>672069</t>
+          <t>705213</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>902641</t>
+          <t>766222</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>721775</t>
+          <t>726964</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1386413</t>
+          <t>803573</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1515979</t>
+          <t>1429302</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1305539</t>
+          <t>1369921</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2162816</t>
+          <t>1483872</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2844598</t>
+          <t>2867772</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2785868</t>
+          <t>2825639</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2989226</t>
+          <t>2912111</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2755392</t>
+          <t>2966423</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2271620</t>
+          <t>2929072</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2936258</t>
+          <t>3005681</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5599990</t>
+          <t>5834195</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4953153</t>
+          <t>5779625</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5810430</t>
+          <t>5893576</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3457937</t>
+          <t>3530852</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3457937</t>
+          <t>3530852</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3457937</t>
+          <t>3530852</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7115969</t>
+          <t>7263497</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7115969</t>
+          <t>7263497</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7115969</t>
+          <t>7263497</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
